--- a/public/exports/29189986.xlsx
+++ b/public/exports/29189986.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289829</t>
+          <t xml:space="preserve">311289859</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289829</t>
+          <t xml:space="preserve">311289859</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6289,12 +6289,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289829</t>
+          <t xml:space="preserve">311289859</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">

--- a/public/exports/29189986.xlsx
+++ b/public/exports/29189986.xlsx
@@ -6139,12 +6139,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289859</t>
+          <t xml:space="preserve">311289829</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289859</t>
+          <t xml:space="preserve">311289829</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6289,12 +6289,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289859</t>
+          <t xml:space="preserve">311289829</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M84" t="inlineStr">
